--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/12-reserva-e-metas-de-caixa.xlsx
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1031,77 +1031,89 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Copie o Painel e use o prompt "Explicar o mês ao sócio" da biblioteca do kit para decidir aporte e metas do próximo trimestre com o sócio.</t>
+          <t>Copie o Painel e use o prompt "Caixa 07 · Plano para a reserva de três meses" da biblioteca do kit para decidir aporte e metas do próximo trimestre com o sócio.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Legenda</t>
+          <t>Números em texto</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
+          <t>A frase "Contando o caixa livre" usa a função FIXED: os separadores seguem o idioma do Excel (em português: R$ 26.062 e 2,1 meses).</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Proteção</t>
+          <t>Legenda</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
+          <t>Células amarelas: você preenche. Brancas: calculadas. Não é preciso mexer em nada fora do amarelo.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Requisitos</t>
+          <t>Proteção</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Excel 2019 ou mais novo, Microsoft 365 ou Google Sheets. No celular abre nos aplicativos; para preencher, use o computador.</t>
+          <t>Fórmulas protegidas sem senha. Para editar: Revisar &gt; Desproteger planilha (Excel) ou Dados &gt; Proteger intervalos (Google Sheets).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1135,9 +1147,9 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5">
+      <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · Reserva e metas de caixa · "&amp;TEXT(DAY(Config!B5),"00")&amp;"/"&amp;TEXT(MONTH(Config!B5),"00")&amp;"/"&amp;YEAR(Config!B5)</f>
-        <v/>
+        <v>Ferraz &amp; Lima Advocacia (exemplo fictício) · Reserva e metas de caixa · 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -1182,27 +1194,27 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="15">
         <f>Config!$B$8*Config!$B$16</f>
-        <v/>
+        <v>55500</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>Config!$B$22</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
         <f>MAX(0,A5-C5)</f>
-        <v/>
+        <v>43500</v>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="18">
         <f>IF(Config!$B$16=0,0,C5/Config!$B$16)</f>
-        <v/>
+        <v>0.648648648648649</v>
       </c>
       <c r="H5" s="14" t="n"/>
-      <c r="I5" s="19">
+      <c r="I5" s="19" t="str">
         <f>IF(C5&gt;=A5,"Já atingida",IFERROR(INDEX(A10:A33,MATCH("Meta atingida",F10:F33,0)),"Depois de 24 meses"))</f>
-        <v/>
+        <v>Dezembro/2027</v>
       </c>
       <c r="J5" s="8" t="n"/>
     </row>
@@ -1212,13 +1224,13 @@
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="21" t="str">
         <f>IF(G5&lt;1,"Vermelho: menos de 1 mês de custo fixo guardado",IF(G5&lt;Config!$B$8,"Amarelo: abaixo da meta",IF(G5&lt;Config!$B$8+1,"Verde: meta atingida","Verde: acima da meta")))</f>
-        <v/>
-      </c>
-      <c r="G7" s="22">
-        <f>"Contando o caixa livre (R$ "&amp;ROUND(Config!$B$21,0)&amp;"): "&amp;ROUND(IF(Config!$B$16=0,0,(C5+Config!$B$21)/Config!$B$16),1)&amp;" meses"</f>
-        <v/>
+        <v>Vermelho: menos de 1 mês de custo fixo guardado</v>
+      </c>
+      <c r="G7" s="22" t="str">
+        <f>"Contando o caixa livre (R$ "&amp;FIXED(Config!$B$21,0)&amp;"): "&amp;FIXED(IF(Config!$B$16=0,0,(C5+Config!$B$21)/Config!$B$16),1)&amp;" meses"</f>
+        <v>Contando o caixa livre (R$ 28,281): 2.2 meses</v>
       </c>
     </row>
     <row r="8">
@@ -1268,867 +1280,867 @@
       <c r="I9" s="26" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27">
+      <c r="A10" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+0-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+0-1)/12))</f>
-        <v/>
+        <v>Outubro/2026</v>
       </c>
       <c r="B10" s="28">
         <f>Config!$B$22</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="C10" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D10" s="29">
         <f>B10+C10</f>
-        <v/>
+        <v>15000</v>
       </c>
       <c r="E10" s="30">
         <f>IF($A$5=0,"",D10/$A$5)</f>
-        <v/>
+        <v>0.27027027027027</v>
       </c>
       <c r="F10" s="31">
         <f>IF(D10&gt;=$A$5,IF(B10&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="32">
+      <c r="G10" s="32" t="str">
         <f>IF(E10="","",REPT("█",ROUND(MIN(1,E10)*30,0)))</f>
-        <v/>
+        <v>████████</v>
       </c>
       <c r="H10" s="25" t="n"/>
       <c r="I10" s="26" t="n"/>
       <c r="J10" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27">
+      <c r="A11" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+1-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+1-1)/12))</f>
-        <v/>
+        <v>Novembro/2026</v>
       </c>
       <c r="B11" s="28">
         <f>D10</f>
-        <v/>
+        <v>15000</v>
       </c>
       <c r="C11" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D11" s="29">
         <f>B11+C11</f>
-        <v/>
+        <v>18000</v>
       </c>
       <c r="E11" s="30">
         <f>IF($A$5=0,"",D11/$A$5)</f>
-        <v/>
+        <v>0.324324324324324</v>
       </c>
       <c r="F11" s="31">
         <f>IF(D11&gt;=$A$5,IF(B11&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="32" t="str">
         <f>IF(E11="","",REPT("█",ROUND(MIN(1,E11)*30,0)))</f>
-        <v/>
+        <v>██████████</v>
       </c>
       <c r="H11" s="25" t="n"/>
       <c r="I11" s="26" t="n"/>
       <c r="J11" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27">
+      <c r="A12" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+2-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+2-1)/12))</f>
-        <v/>
+        <v>Dezembro/2026</v>
       </c>
       <c r="B12" s="28">
         <f>D11</f>
-        <v/>
+        <v>18000</v>
       </c>
       <c r="C12" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D12" s="29">
         <f>B12+C12</f>
-        <v/>
+        <v>21000</v>
       </c>
       <c r="E12" s="30">
         <f>IF($A$5=0,"",D12/$A$5)</f>
-        <v/>
+        <v>0.378378378378378</v>
       </c>
       <c r="F12" s="31">
         <f>IF(D12&gt;=$A$5,IF(B12&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="32" t="str">
         <f>IF(E12="","",REPT("█",ROUND(MIN(1,E12)*30,0)))</f>
-        <v/>
+        <v>███████████</v>
       </c>
       <c r="H12" s="25" t="n"/>
       <c r="I12" s="26" t="n"/>
       <c r="J12" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27">
+      <c r="A13" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+3-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+3-1)/12))</f>
-        <v/>
+        <v>Janeiro/2027</v>
       </c>
       <c r="B13" s="28">
         <f>D12</f>
-        <v/>
+        <v>21000</v>
       </c>
       <c r="C13" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D13" s="29">
         <f>B13+C13</f>
-        <v/>
+        <v>24000</v>
       </c>
       <c r="E13" s="30">
         <f>IF($A$5=0,"",D13/$A$5)</f>
-        <v/>
+        <v>0.432432432432432</v>
       </c>
       <c r="F13" s="31">
         <f>IF(D13&gt;=$A$5,IF(B13&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="32" t="str">
         <f>IF(E13="","",REPT("█",ROUND(MIN(1,E13)*30,0)))</f>
-        <v/>
+        <v>█████████████</v>
       </c>
       <c r="H13" s="25" t="n"/>
       <c r="I13" s="26" t="n"/>
       <c r="J13" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27">
+      <c r="A14" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+4-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+4-1)/12))</f>
-        <v/>
+        <v>Fevereiro/2027</v>
       </c>
       <c r="B14" s="28">
         <f>D13</f>
-        <v/>
+        <v>24000</v>
       </c>
       <c r="C14" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D14" s="29">
         <f>B14+C14</f>
-        <v/>
+        <v>27000</v>
       </c>
       <c r="E14" s="30">
         <f>IF($A$5=0,"",D14/$A$5)</f>
-        <v/>
+        <v>0.486486486486487</v>
       </c>
       <c r="F14" s="31">
         <f>IF(D14&gt;=$A$5,IF(B14&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="32" t="str">
         <f>IF(E14="","",REPT("█",ROUND(MIN(1,E14)*30,0)))</f>
-        <v/>
+        <v>███████████████</v>
       </c>
       <c r="H14" s="25" t="n"/>
       <c r="I14" s="26" t="n"/>
       <c r="J14" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27">
+      <c r="A15" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+5-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+5-1)/12))</f>
-        <v/>
+        <v>Março/2027</v>
       </c>
       <c r="B15" s="28">
         <f>D14</f>
-        <v/>
+        <v>27000</v>
       </c>
       <c r="C15" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D15" s="29">
         <f>B15+C15</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="E15" s="30">
         <f>IF($A$5=0,"",D15/$A$5)</f>
-        <v/>
+        <v>0.540540540540541</v>
       </c>
       <c r="F15" s="31">
         <f>IF(D15&gt;=$A$5,IF(B15&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G15" s="32">
+      <c r="G15" s="32" t="str">
         <f>IF(E15="","",REPT("█",ROUND(MIN(1,E15)*30,0)))</f>
-        <v/>
+        <v>████████████████</v>
       </c>
       <c r="H15" s="25" t="n"/>
       <c r="I15" s="26" t="n"/>
       <c r="J15" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27">
+      <c r="A16" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+6-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+6-1)/12))</f>
-        <v/>
+        <v>Abril/2027</v>
       </c>
       <c r="B16" s="28">
         <f>D15</f>
-        <v/>
+        <v>30000</v>
       </c>
       <c r="C16" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D16" s="29">
         <f>B16+C16</f>
-        <v/>
+        <v>33000</v>
       </c>
       <c r="E16" s="30">
         <f>IF($A$5=0,"",D16/$A$5)</f>
-        <v/>
+        <v>0.594594594594595</v>
       </c>
       <c r="F16" s="31">
         <f>IF(D16&gt;=$A$5,IF(B16&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G16" s="32">
+      <c r="G16" s="32" t="str">
         <f>IF(E16="","",REPT("█",ROUND(MIN(1,E16)*30,0)))</f>
-        <v/>
+        <v>██████████████████</v>
       </c>
       <c r="H16" s="25" t="n"/>
       <c r="I16" s="26" t="n"/>
       <c r="J16" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="27">
+      <c r="A17" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+7-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+7-1)/12))</f>
-        <v/>
+        <v>Maio/2027</v>
       </c>
       <c r="B17" s="28">
         <f>D16</f>
-        <v/>
+        <v>33000</v>
       </c>
       <c r="C17" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D17" s="29">
         <f>B17+C17</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="E17" s="30">
         <f>IF($A$5=0,"",D17/$A$5)</f>
-        <v/>
+        <v>0.648648648648649</v>
       </c>
       <c r="F17" s="31">
         <f>IF(D17&gt;=$A$5,IF(B17&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G17" s="32">
+      <c r="G17" s="32" t="str">
         <f>IF(E17="","",REPT("█",ROUND(MIN(1,E17)*30,0)))</f>
-        <v/>
+        <v>███████████████████</v>
       </c>
       <c r="H17" s="25" t="n"/>
       <c r="I17" s="26" t="n"/>
       <c r="J17" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27">
+      <c r="A18" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+8-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+8-1)/12))</f>
-        <v/>
+        <v>Junho/2027</v>
       </c>
       <c r="B18" s="28">
         <f>D17</f>
-        <v/>
+        <v>36000</v>
       </c>
       <c r="C18" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D18" s="29">
         <f>B18+C18</f>
-        <v/>
+        <v>39000</v>
       </c>
       <c r="E18" s="30">
         <f>IF($A$5=0,"",D18/$A$5)</f>
-        <v/>
+        <v>0.702702702702703</v>
       </c>
       <c r="F18" s="31">
         <f>IF(D18&gt;=$A$5,IF(B18&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G18" s="32">
+      <c r="G18" s="32" t="str">
         <f>IF(E18="","",REPT("█",ROUND(MIN(1,E18)*30,0)))</f>
-        <v/>
+        <v>█████████████████████</v>
       </c>
       <c r="H18" s="25" t="n"/>
       <c r="I18" s="26" t="n"/>
       <c r="J18" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="27">
+      <c r="A19" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+9-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+9-1)/12))</f>
-        <v/>
+        <v>Julho/2027</v>
       </c>
       <c r="B19" s="28">
         <f>D18</f>
-        <v/>
+        <v>39000</v>
       </c>
       <c r="C19" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D19" s="29">
         <f>B19+C19</f>
-        <v/>
+        <v>42000</v>
       </c>
       <c r="E19" s="30">
         <f>IF($A$5=0,"",D19/$A$5)</f>
-        <v/>
+        <v>0.756756756756757</v>
       </c>
       <c r="F19" s="31">
         <f>IF(D19&gt;=$A$5,IF(B19&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="32" t="str">
         <f>IF(E19="","",REPT("█",ROUND(MIN(1,E19)*30,0)))</f>
-        <v/>
+        <v>███████████████████████</v>
       </c>
       <c r="H19" s="25" t="n"/>
       <c r="I19" s="26" t="n"/>
       <c r="J19" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="27">
+      <c r="A20" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+10-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+10-1)/12))</f>
-        <v/>
+        <v>Agosto/2027</v>
       </c>
       <c r="B20" s="28">
         <f>D19</f>
-        <v/>
+        <v>42000</v>
       </c>
       <c r="C20" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D20" s="29">
         <f>B20+C20</f>
-        <v/>
+        <v>45000</v>
       </c>
       <c r="E20" s="30">
         <f>IF($A$5=0,"",D20/$A$5)</f>
-        <v/>
+        <v>0.810810810810811</v>
       </c>
       <c r="F20" s="31">
         <f>IF(D20&gt;=$A$5,IF(B20&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G20" s="32">
+      <c r="G20" s="32" t="str">
         <f>IF(E20="","",REPT("█",ROUND(MIN(1,E20)*30,0)))</f>
-        <v/>
+        <v>████████████████████████</v>
       </c>
       <c r="H20" s="25" t="n"/>
       <c r="I20" s="26" t="n"/>
       <c r="J20" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="27">
+      <c r="A21" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+11-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+11-1)/12))</f>
-        <v/>
+        <v>Setembro/2027</v>
       </c>
       <c r="B21" s="28">
         <f>D20</f>
-        <v/>
+        <v>45000</v>
       </c>
       <c r="C21" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D21" s="29">
         <f>B21+C21</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="E21" s="30">
         <f>IF($A$5=0,"",D21/$A$5)</f>
-        <v/>
+        <v>0.864864864864865</v>
       </c>
       <c r="F21" s="31">
         <f>IF(D21&gt;=$A$5,IF(B21&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="32" t="str">
         <f>IF(E21="","",REPT("█",ROUND(MIN(1,E21)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████</v>
       </c>
       <c r="H21" s="25" t="n"/>
       <c r="I21" s="26" t="n"/>
       <c r="J21" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="27">
+      <c r="A22" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+12-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+12-1)/12))</f>
-        <v/>
+        <v>Outubro/2027</v>
       </c>
       <c r="B22" s="28">
         <f>D21</f>
-        <v/>
+        <v>48000</v>
       </c>
       <c r="C22" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D22" s="29">
         <f>B22+C22</f>
-        <v/>
+        <v>51000</v>
       </c>
       <c r="E22" s="30">
         <f>IF($A$5=0,"",D22/$A$5)</f>
-        <v/>
+        <v>0.918918918918919</v>
       </c>
       <c r="F22" s="31">
         <f>IF(D22&gt;=$A$5,IF(B22&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="32" t="str">
         <f>IF(E22="","",REPT("█",ROUND(MIN(1,E22)*30,0)))</f>
-        <v/>
+        <v>████████████████████████████</v>
       </c>
       <c r="H22" s="25" t="n"/>
       <c r="I22" s="26" t="n"/>
       <c r="J22" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="27">
+      <c r="A23" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+13-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+13-1)/12))</f>
-        <v/>
+        <v>Novembro/2027</v>
       </c>
       <c r="B23" s="28">
         <f>D22</f>
-        <v/>
+        <v>51000</v>
       </c>
       <c r="C23" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D23" s="29">
         <f>B23+C23</f>
-        <v/>
+        <v>54000</v>
       </c>
       <c r="E23" s="30">
         <f>IF($A$5=0,"",D23/$A$5)</f>
-        <v/>
+        <v>0.972972972972973</v>
       </c>
       <c r="F23" s="31">
         <f>IF(D23&gt;=$A$5,IF(B23&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
         <v/>
       </c>
-      <c r="G23" s="32">
+      <c r="G23" s="32" t="str">
         <f>IF(E23="","",REPT("█",ROUND(MIN(1,E23)*30,0)))</f>
-        <v/>
+        <v>█████████████████████████████</v>
       </c>
       <c r="H23" s="25" t="n"/>
       <c r="I23" s="26" t="n"/>
       <c r="J23" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27">
+      <c r="A24" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+14-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+14-1)/12))</f>
-        <v/>
+        <v>Dezembro/2027</v>
       </c>
       <c r="B24" s="28">
         <f>D23</f>
-        <v/>
+        <v>54000</v>
       </c>
       <c r="C24" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D24" s="29">
         <f>B24+C24</f>
-        <v/>
+        <v>57000</v>
       </c>
       <c r="E24" s="30">
         <f>IF($A$5=0,"",D24/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F24" s="31">
+        <v>1.02702702702703</v>
+      </c>
+      <c r="F24" s="31" t="str">
         <f>IF(D24&gt;=$A$5,IF(B24&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="32">
+        <v>Meta atingida</v>
+      </c>
+      <c r="G24" s="32" t="str">
         <f>IF(E24="","",REPT("█",ROUND(MIN(1,E24)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H24" s="25" t="n"/>
       <c r="I24" s="26" t="n"/>
       <c r="J24" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="27">
+      <c r="A25" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+15-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+15-1)/12))</f>
-        <v/>
+        <v>Janeiro/2028</v>
       </c>
       <c r="B25" s="28">
         <f>D24</f>
-        <v/>
+        <v>57000</v>
       </c>
       <c r="C25" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D25" s="29">
         <f>B25+C25</f>
-        <v/>
+        <v>60000</v>
       </c>
       <c r="E25" s="30">
         <f>IF($A$5=0,"",D25/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F25" s="31">
+        <v>1.08108108108108</v>
+      </c>
+      <c r="F25" s="31" t="str">
         <f>IF(D25&gt;=$A$5,IF(B25&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G25" s="32" t="str">
         <f>IF(E25="","",REPT("█",ROUND(MIN(1,E25)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H25" s="25" t="n"/>
       <c r="I25" s="26" t="n"/>
       <c r="J25" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="27">
+      <c r="A26" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+16-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+16-1)/12))</f>
-        <v/>
+        <v>Fevereiro/2028</v>
       </c>
       <c r="B26" s="28">
         <f>D25</f>
-        <v/>
+        <v>60000</v>
       </c>
       <c r="C26" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D26" s="29">
         <f>B26+C26</f>
-        <v/>
+        <v>63000</v>
       </c>
       <c r="E26" s="30">
         <f>IF($A$5=0,"",D26/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F26" s="31">
+        <v>1.13513513513514</v>
+      </c>
+      <c r="F26" s="31" t="str">
         <f>IF(D26&gt;=$A$5,IF(B26&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G26" s="32" t="str">
         <f>IF(E26="","",REPT("█",ROUND(MIN(1,E26)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H26" s="25" t="n"/>
       <c r="I26" s="26" t="n"/>
       <c r="J26" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="27">
+      <c r="A27" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+17-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+17-1)/12))</f>
-        <v/>
+        <v>Março/2028</v>
       </c>
       <c r="B27" s="28">
         <f>D26</f>
-        <v/>
+        <v>63000</v>
       </c>
       <c r="C27" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D27" s="29">
         <f>B27+C27</f>
-        <v/>
+        <v>66000</v>
       </c>
       <c r="E27" s="30">
         <f>IF($A$5=0,"",D27/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F27" s="31">
+        <v>1.18918918918919</v>
+      </c>
+      <c r="F27" s="31" t="str">
         <f>IF(D27&gt;=$A$5,IF(B27&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G27" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G27" s="32" t="str">
         <f>IF(E27="","",REPT("█",ROUND(MIN(1,E27)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H27" s="25" t="n"/>
       <c r="I27" s="26" t="n"/>
       <c r="J27" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="27">
+      <c r="A28" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+18-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+18-1)/12))</f>
-        <v/>
+        <v>Abril/2028</v>
       </c>
       <c r="B28" s="28">
         <f>D27</f>
-        <v/>
+        <v>66000</v>
       </c>
       <c r="C28" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D28" s="29">
         <f>B28+C28</f>
-        <v/>
+        <v>69000</v>
       </c>
       <c r="E28" s="30">
         <f>IF($A$5=0,"",D28/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F28" s="31">
+        <v>1.24324324324324</v>
+      </c>
+      <c r="F28" s="31" t="str">
         <f>IF(D28&gt;=$A$5,IF(B28&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G28" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G28" s="32" t="str">
         <f>IF(E28="","",REPT("█",ROUND(MIN(1,E28)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H28" s="25" t="n"/>
       <c r="I28" s="26" t="n"/>
       <c r="J28" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="27">
+      <c r="A29" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+19-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+19-1)/12))</f>
-        <v/>
+        <v>Maio/2028</v>
       </c>
       <c r="B29" s="28">
         <f>D28</f>
-        <v/>
+        <v>69000</v>
       </c>
       <c r="C29" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D29" s="29">
         <f>B29+C29</f>
-        <v/>
+        <v>72000</v>
       </c>
       <c r="E29" s="30">
         <f>IF($A$5=0,"",D29/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F29" s="31">
+        <v>1.2972972972973</v>
+      </c>
+      <c r="F29" s="31" t="str">
         <f>IF(D29&gt;=$A$5,IF(B29&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G29" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G29" s="32" t="str">
         <f>IF(E29="","",REPT("█",ROUND(MIN(1,E29)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H29" s="25" t="n"/>
       <c r="I29" s="26" t="n"/>
       <c r="J29" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="27">
+      <c r="A30" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+20-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+20-1)/12))</f>
-        <v/>
+        <v>Junho/2028</v>
       </c>
       <c r="B30" s="28">
         <f>D29</f>
-        <v/>
+        <v>72000</v>
       </c>
       <c r="C30" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D30" s="29">
         <f>B30+C30</f>
-        <v/>
+        <v>75000</v>
       </c>
       <c r="E30" s="30">
         <f>IF($A$5=0,"",D30/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F30" s="31">
+        <v>1.35135135135135</v>
+      </c>
+      <c r="F30" s="31" t="str">
         <f>IF(D30&gt;=$A$5,IF(B30&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G30" s="32" t="str">
         <f>IF(E30="","",REPT("█",ROUND(MIN(1,E30)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H30" s="25" t="n"/>
       <c r="I30" s="26" t="n"/>
       <c r="J30" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="27">
+      <c r="A31" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+21-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+21-1)/12))</f>
-        <v/>
+        <v>Julho/2028</v>
       </c>
       <c r="B31" s="28">
         <f>D30</f>
-        <v/>
+        <v>75000</v>
       </c>
       <c r="C31" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D31" s="29">
         <f>B31+C31</f>
-        <v/>
+        <v>78000</v>
       </c>
       <c r="E31" s="30">
         <f>IF($A$5=0,"",D31/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F31" s="31">
+        <v>1.40540540540541</v>
+      </c>
+      <c r="F31" s="31" t="str">
         <f>IF(D31&gt;=$A$5,IF(B31&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G31" s="32" t="str">
         <f>IF(E31="","",REPT("█",ROUND(MIN(1,E31)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H31" s="25" t="n"/>
       <c r="I31" s="26" t="n"/>
       <c r="J31" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27">
+      <c r="A32" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+22-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+22-1)/12))</f>
-        <v/>
+        <v>Agosto/2028</v>
       </c>
       <c r="B32" s="28">
         <f>D31</f>
-        <v/>
+        <v>78000</v>
       </c>
       <c r="C32" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D32" s="29">
         <f>B32+C32</f>
-        <v/>
+        <v>81000</v>
       </c>
       <c r="E32" s="30">
         <f>IF($A$5=0,"",D32/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F32" s="31">
+        <v>1.45945945945946</v>
+      </c>
+      <c r="F32" s="31" t="str">
         <f>IF(D32&gt;=$A$5,IF(B32&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G32" s="32" t="str">
         <f>IF(E32="","",REPT("█",ROUND(MIN(1,E32)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H32" s="25" t="n"/>
       <c r="I32" s="26" t="n"/>
       <c r="J32" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="27">
+      <c r="A33" s="27" t="str">
         <f>INDEX(Config!$H$5:$H$16,MOD(MATCH(Config!$B$6,Config!$H$5:$H$16,0)+23-1,12)+1)&amp;"/"&amp;(Config!$B$7+INT((MATCH(Config!$B$6,Config!$H$5:$H$16,0)+23-1)/12))</f>
-        <v/>
+        <v>Setembro/2028</v>
       </c>
       <c r="B33" s="28">
         <f>D32</f>
-        <v/>
+        <v>81000</v>
       </c>
       <c r="C33" s="28">
         <f>Config!$B$9</f>
-        <v/>
+        <v>3000</v>
       </c>
       <c r="D33" s="29">
         <f>B33+C33</f>
-        <v/>
+        <v>84000</v>
       </c>
       <c r="E33" s="30">
         <f>IF($A$5=0,"",D33/$A$5)</f>
-        <v/>
-      </c>
-      <c r="F33" s="31">
+        <v>1.51351351351351</v>
+      </c>
+      <c r="F33" s="31" t="str">
         <f>IF(D33&gt;=$A$5,IF(B33&lt;$A$5,"Meta atingida","Acima da meta"),"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="32">
+        <v>Acima da meta</v>
+      </c>
+      <c r="G33" s="32" t="str">
         <f>IF(E33="","",REPT("█",ROUND(MIN(1,E33)*30,0)))</f>
-        <v/>
+        <v>██████████████████████████████</v>
       </c>
       <c r="H33" s="25" t="n"/>
       <c r="I33" s="26" t="n"/>
       <c r="J33" s="33">
         <f>$A$5</f>
-        <v/>
+        <v>55500</v>
       </c>
     </row>
     <row r="34">
@@ -2188,105 +2200,105 @@
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="34">
+      <c r="A37" s="34" t="str">
         <f>IF(Config!$A$26="","",Config!$A$26)</f>
-        <v/>
+        <v>Reserva com 1 mês de custo fixo</v>
       </c>
       <c r="B37" s="28">
         <f>IF(Config!$A$26="","",Config!$B$26)</f>
-        <v/>
+        <v>18500</v>
       </c>
       <c r="C37" s="28">
         <f>IF(Config!$A$26="","",Config!$C$26)</f>
-        <v/>
+        <v>12000</v>
       </c>
       <c r="D37" s="30">
         <f>IF(OR(Config!$A$26="",B37=0),"",MIN(1,C37/B37))</f>
-        <v/>
-      </c>
-      <c r="E37" s="32">
+        <v>0.648648648648649</v>
+      </c>
+      <c r="E37" s="32" t="str">
         <f>IF(D37="","",REPT("█",ROUND(D37*20,0)))</f>
-        <v/>
+        <v>█████████████</v>
       </c>
       <c r="F37" s="35">
         <f>IF(OR(Config!$A$26="",Config!$D$26=""),"",Config!$D$26)</f>
-        <v/>
+        <v>46387.0</v>
       </c>
       <c r="G37" s="36">
         <f>IF(OR(Config!$A$26="",F37="",H37="Concluída"),"",F37-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H37" s="31">
+        <v>108</v>
+      </c>
+      <c r="H37" s="31" t="str">
         <f>IF(Config!$A$26="","",IF(AND(B37&gt;0,C37&gt;=B37),"Concluída",IF(AND(F37&lt;&gt;"",F37&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
-        <v/>
+        <v>Em andamento</v>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="34">
+      <c r="A38" s="34" t="str">
         <f>IF(Config!$A$27="","",Config!$A$27)</f>
-        <v/>
+        <v>Receber R$ 75.000 no trimestre</v>
       </c>
       <c r="B38" s="28">
         <f>IF(Config!$A$27="","",Config!$B$27)</f>
-        <v/>
+        <v>75000</v>
       </c>
       <c r="C38" s="28">
         <f>IF(Config!$A$27="","",Config!$C$27)</f>
-        <v/>
+        <v>61580</v>
       </c>
       <c r="D38" s="30">
         <f>IF(OR(Config!$A$27="",B38=0),"",MIN(1,C38/B38))</f>
-        <v/>
-      </c>
-      <c r="E38" s="32">
+        <v>0.821066666666667</v>
+      </c>
+      <c r="E38" s="32" t="str">
         <f>IF(D38="","",REPT("█",ROUND(D38*20,0)))</f>
-        <v/>
+        <v>████████████████</v>
       </c>
       <c r="F38" s="35">
         <f>IF(OR(Config!$A$27="",Config!$D$27=""),"",Config!$D$27)</f>
-        <v/>
+        <v>46295.0</v>
       </c>
       <c r="G38" s="36">
         <f>IF(OR(Config!$A$27="",F38="",H38="Concluída"),"",F38-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H38" s="31">
+        <v>16</v>
+      </c>
+      <c r="H38" s="31" t="str">
         <f>IF(Config!$A$27="","",IF(AND(B38&gt;0,C38&gt;=B38),"Concluída",IF(AND(F38&lt;&gt;"",F38&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
-        <v/>
+        <v>Em andamento</v>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="34">
+      <c r="A39" s="34" t="str">
         <f>IF(Config!$A$28="","",Config!$A$28)</f>
-        <v/>
+        <v>Conta de provisão de impostos com o saldo da planilha 10</v>
       </c>
       <c r="B39" s="28">
         <f>IF(Config!$A$28="","",Config!$B$28)</f>
-        <v/>
+        <v>11320</v>
       </c>
       <c r="C39" s="28">
         <f>IF(Config!$A$28="","",Config!$C$28)</f>
-        <v/>
+        <v>9400</v>
       </c>
       <c r="D39" s="30">
         <f>IF(OR(Config!$A$28="",B39=0),"",MIN(1,C39/B39))</f>
-        <v/>
-      </c>
-      <c r="E39" s="32">
+        <v>0.830388692579505</v>
+      </c>
+      <c r="E39" s="32" t="str">
         <f>IF(D39="","",REPT("█",ROUND(D39*20,0)))</f>
-        <v/>
+        <v>█████████████████</v>
       </c>
       <c r="F39" s="35">
         <f>IF(OR(Config!$A$28="",Config!$D$28=""),"",Config!$D$28)</f>
-        <v/>
+        <v>46295.0</v>
       </c>
       <c r="G39" s="36">
         <f>IF(OR(Config!$A$28="",F39="",H39="Concluída"),"",F39-Config!$B$5)</f>
-        <v/>
-      </c>
-      <c r="H39" s="31">
+        <v>16</v>
+      </c>
+      <c r="H39" s="31" t="str">
         <f>IF(Config!$A$28="","",IF(AND(B39&gt;0,C39&gt;=B39),"Concluída",IF(AND(F39&lt;&gt;"",F39&lt;Config!$B$5),"Prazo vencido","Em andamento")))</f>
-        <v/>
+        <v>Em andamento</v>
       </c>
     </row>
     <row r="40">
@@ -2429,7 +2441,7 @@
       </c>
       <c r="B5" s="35">
         <f>TODAY()</f>
-        <v/>
+        <v>46279.0</v>
       </c>
       <c r="H5" s="38" t="inlineStr">
         <is>
@@ -2598,7 +2610,7 @@
       </c>
       <c r="B16" s="43">
         <f>IFERROR(AVERAGE(B13:B15),0)</f>
-        <v/>
+        <v>18500</v>
       </c>
       <c r="H16" s="38" t="inlineStr">
         <is>
@@ -2620,11 +2632,11 @@
         </is>
       </c>
       <c r="B19" s="41" t="n">
-        <v>40795</v>
+        <v>43683</v>
       </c>
       <c r="D19" s="22" t="inlineStr">
         <is>
-          <t>Saldo acumulado e A pagar do Painel da planilha 09.</t>
+          <t>Saldo acumulado (setembro) e A pagar do Painel da planilha 09, em 14/09/2026.</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2647,7 @@
         </is>
       </c>
       <c r="B20" s="41" t="n">
-        <v>14733</v>
+        <v>15402</v>
       </c>
     </row>
     <row r="21">
@@ -2646,7 +2658,7 @@
       </c>
       <c r="B21" s="44">
         <f>B19-B20</f>
-        <v/>
+        <v>28281</v>
       </c>
     </row>
     <row r="22">
@@ -2705,26 +2717,24 @@
       <c r="C26" s="41" t="n">
         <v>12000</v>
       </c>
-      <c r="D26" s="45">
-        <f>TODAY()+108</f>
-        <v/>
+      <c r="D26" s="45" t="n">
+        <v>46387</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="37" t="inlineStr">
         <is>
-          <t>Receber R$ 65.000 no trimestre</t>
+          <t>Receber R$ 75.000 no trimestre</t>
         </is>
       </c>
       <c r="B27" s="41" t="n">
-        <v>65000</v>
+        <v>75000</v>
       </c>
       <c r="C27" s="41" t="n">
-        <v>67630</v>
-      </c>
-      <c r="D27" s="45">
-        <f>TODAY()+16</f>
-        <v/>
+        <v>61580</v>
+      </c>
+      <c r="D27" s="45" t="n">
+        <v>46295</v>
       </c>
     </row>
     <row r="28">
@@ -2734,20 +2744,19 @@
         </is>
       </c>
       <c r="B28" s="41" t="n">
-        <v>11750</v>
+        <v>11320</v>
       </c>
       <c r="C28" s="41" t="n">
         <v>9400</v>
       </c>
-      <c r="D28" s="45">
-        <f>TODAY()+16</f>
-        <v/>
+      <c r="D28" s="45" t="n">
+        <v>46295</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>Metas que se medem em reais e crescem até o alvo (reserva, recebimentos, provisão separada). Atualize o valor atual toda sexta. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Metas que se medem em reais e crescem até o alvo (reserva, recebimentos, provisão separada). Atualize o valor atual toda sexta. No exemplo os prazos são datas fixas (fim do trimestre e do ano).</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/12-reserva-e-metas-de-caixa.xlsx
@@ -18,11 +18,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
+  <numFmts count="5">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;R$&quot; #,##0.00;[Red]-&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;R$&quot; #,##0;[Red]-&quot;R$&quot; #,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -272,16 +273,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,10 +298,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -310,13 +311,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -334,19 +335,19 @@
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -942,7 +943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1043,7 +1044,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>A frase "Contando o caixa livre" usa a função FIXED: os separadores seguem o idioma do Excel (em português: R$ 26.062 e 2,1 meses).</t>
+          <t>A frase "Contando o caixa livre" usa a função FIXED: os separadores seguem o idioma do Excel (em português, ponto no milhar e vírgula no decimal). O valor vem do Painel; não está escrito aqui, para não envelhecer a cada lançamento.</t>
         </is>
       </c>
     </row>
@@ -1103,17 +1104,29 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar. Datas de prazo do exemplo são relativas a hoje.</t>
+          <t>Ferraz &amp; Lima Advocacia é um escritório fictício. Clientes, processos, nomes e valores são inventados. Apague-os antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1230,7 +1243,7 @@
       </c>
       <c r="G7" s="22" t="str">
         <f>"Contando o caixa livre (R$ "&amp;FIXED(Config!$B$21,0)&amp;"): "&amp;FIXED(IF(Config!$B$16=0,0,(C5+Config!$B$21)/Config!$B$16),1)&amp;" meses"</f>
-        <v>Contando o caixa livre (R$ 28,281): 2.2 meses</v>
+        <v>Contando o caixa livre (R$ 28.281): 2,2 meses</v>
       </c>
     </row>
     <row r="8">
@@ -2439,9 +2452,8 @@
           <t>Data de referência</t>
         </is>
       </c>
-      <c r="B5" s="35">
-        <f>TODAY()</f>
-        <v>46279.0</v>
+      <c r="B5" s="35" t="n">
+        <v>46279</v>
       </c>
       <c r="H5" s="38" t="inlineStr">
         <is>
@@ -2771,7 +2783,7 @@
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$H$5:$H$16</formula1>
     </dataValidation>
-    <dataValidation sqref="D26:D28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D26:D28" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/12-reserva-e-metas-de-caixa.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-advogados/entrega/12-reserva-e-metas-de-caixa.xlsx
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
